--- a/data/b2_indio/B2 Índio 08-2026.xlsx
+++ b/data/b2_indio/B2 Índio 08-2026.xlsx
@@ -4918,25 +4918,25 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>812.96</v>
+        <v>863.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1840.45</v>
+        <v>51642.87</v>
       </c>
     </row>
     <row r="4">
@@ -4945,88 +4945,88 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>52727.76</v>
+        <v>2791.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3110.84</v>
+        <v>1844.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3900</v>
+        <v>3218.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1942.6</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>10016.86</v>
+        <v>2001.51</v>
       </c>
     </row>
     <row r="9">
@@ -5035,16 +5035,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1392.54</v>
+        <v>9041.49</v>
       </c>
     </row>
     <row r="10">
@@ -5053,93 +5053,93 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1457.86</v>
+        <v>1573.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>3185.16</v>
+        <v>1185.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>674.77</v>
+        <v>3333.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>18215.85</v>
+        <v>988.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46257</v>
+        <v>46254</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3190.24</v>
+        <v>18185.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5148,29 +5148,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1848.87</v>
+        <v>2917.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46259</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>4004.49</v>
+        <v>3252.88</v>
       </c>
     </row>
     <row r="17">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3175.77</v>
+        <v>3072.64</v>
       </c>
     </row>
     <row r="18">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>451.27</v>
+        <v>450.01</v>
       </c>
     </row>
   </sheetData>
